--- a/Data_clean/MCAS/Estados_US/Edos_USA_2020/WEST_VIRGINIA_2020.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2020/WEST_VIRGINIA_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -454,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -537,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -553,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C14">
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -607,12 +667,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C18">
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>León</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -713,7 +798,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C25">
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -851,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C35">
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -952,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rojas de Cuauhtémoc</t>
+          <t>Rojas De Cuauhtémoc</t>
         </is>
       </c>
       <c r="C42">
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Santos Reyes Pápalo</t>
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1066,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1097,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -1110,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1141,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1172,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1203,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -1216,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1247,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -1260,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -1273,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -1286,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -1299,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1322,41 +1557,6 @@
       </c>
       <c r="D67">
         <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
